--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 75分钟</t>
+          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 26分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +689,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -753,24 +757,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -809,7 +813,7 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -829,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -872,22 +876,26 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -895,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,17 +927,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -939,13 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -953,24 +965,24 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -983,30 +995,34 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1030,17 +1046,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1050,13 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1084,7 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1074,7 +1094,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1112,12 +1132,12 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1131,7 +1151,7 @@
       <c r="T6" s="2" t="inlineStr"/>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1167,7 +1187,1308 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/5</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>111分钟</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站金高路俱进路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>114分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,27 +637,31 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:46</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -714,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -752,29 +756,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -784,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -808,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -823,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -876,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±14分钟</t>
+          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数16分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -942,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -990,29 +994,29 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,12 +1050,12 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1061,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1220,29 +1224,29 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,12 +1280,12 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1291,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1344,24 +1348,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>111分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站金高路俱进路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±11分钟</t>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,7 +1399,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
@@ -1420,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1463,26 +1467,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1582,24 +1582,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>114分钟</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±11分钟</t>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1701,24 +1701,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±10分钟</t>
+          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1820,22 +1820,26 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1867,17 +1871,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1887,13 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1931,24 +1939,24 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±11分钟</t>
+          <t>08:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1958,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1987,7 +1995,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2007,12 +2015,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2050,24 +2058,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±9分钟</t>
+          <t>08:20采样：该车到重点站金高路行泰路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2077,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2106,7 +2114,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2126,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2174,19 +2182,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±8分钟</t>
+          <t>08:20采样：该车到重点站金高路东靖路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2196,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2225,7 +2233,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2245,12 +2253,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2288,19 +2296,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±6分钟</t>
+          <t>08:20采样：该车到重点站五莲路凌河路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2315,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2344,7 +2352,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2364,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2377,24 +2385,24 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66373D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2407,34 +2415,30 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2448,47 +2452,991 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站张杨北路金桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>08:20采样：该车到重点站花山路大同路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数93分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -875,29 +875,29 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数16分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1343,29 +1343,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1472,17 +1472,21 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,12 +1518,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1539,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1582,26 +1586,22 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>111分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1696,29 +1696,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1820,24 +1820,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±9分钟</t>
+          <t>08:40采样：该车到重点站丁香路金松路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2058,26 +2058,22 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金高路行泰路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 30分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -2085,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,12 +2105,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2124,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2177,19 +2173,19 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金高路东靖路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
+          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2204,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2253,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2296,19 +2292,19 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站五莲路凌河路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±6分钟</t>
+          <t>08:40采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2323,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2526,24 +2522,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站张杨北路金桥路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>08:40采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2553,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2602,7 +2598,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2645,24 +2641,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站花山路大同路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±10分钟</t>
+          <t>08:40采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2672,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2721,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2764,24 +2760,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数93分钟估算，约±15分钟</t>
+          <t>08:40采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2791,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2820,7 +2816,7 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2840,12 +2836,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2883,24 +2879,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±9分钟</t>
+          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2910,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2939,7 +2935,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2959,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3121,24 +3117,24 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3148,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3172,12 +3168,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3197,7 +3193,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3267,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3316,12 +3312,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,10 +3427,478 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>96.0</t>
         </is>
       </c>
-      <c r="AC25" s="2" t="inlineStr">
+      <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>8/18</t>
         </is>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1581,27 +1581,31 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1633,12 +1637,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1658,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1701,24 +1705,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1820,26 +1824,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站丁香路金松路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数6分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:50采样，终点ETA 24分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1939,26 +1939,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站五莲路归昌路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:00采样，终点ETA 18分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -1966,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1990,12 +1986,12 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2005,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2053,27 +2049,31 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:40采样，终点ETA 30分钟</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2168,24 +2168,24 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2287,29 +2287,29 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数40分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2411,19 +2411,19 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 26分钟</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr"/>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2458,17 +2458,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2478,13 +2478,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2522,26 +2526,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2641,24 +2641,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>09:10采样：该车到重点站金杨路金桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2760,24 +2760,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站杨高北路夏碧路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±13分钟</t>
+          <t>09:10采样：该车到重点站五莲路凌河路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2879,24 +2879,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±7分钟</t>
+          <t>09:10采样：该车到重点站金高路东靖路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2998,24 +2998,24 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±6分钟</t>
+          <t>08:50采样：该车到重点站航津路地铁站 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3117,19 +3117,19 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>08:40采样：该车到重点站五莲路荷泽路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
+          <t>09:10采样：该车到重点站金高路东靖路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3236,24 +3236,24 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+          <t>09:10采样：该车到重点站张杨北路博兴路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3355,22 +3355,26 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>09:10采样：该车到重点站金高路行泰路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3402,17 +3406,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3422,17 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3470,22 +3474,26 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>09:10采样：该车到重点站张杨北路博兴路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -3493,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3517,17 +3525,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3537,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3585,22 +3593,26 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>09:10采样：该车到重点站金高路行泰路 ETA 47分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3608,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3632,17 +3644,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3652,17 +3664,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3700,24 +3712,24 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±11分钟</t>
+          <t>09:10采样：该车到重点站丁香路长柳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3727,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3751,12 +3763,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3776,12 +3788,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3789,24 +3801,24 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3819,34 +3831,34 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3860,47 +3872,519 @@
       <c r="T29" s="2" t="inlineStr"/>
       <c r="U29" s="2" t="inlineStr">
         <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W29" s="2" t="inlineStr">
+      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="X29" s="2" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr">
-        <is>
-          <t>8/18</t>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2292,24 +2292,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2406,27 +2406,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2458,12 +2462,12 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
@@ -2473,22 +2477,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2521,27 +2525,31 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2549,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2573,12 +2581,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2598,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2636,29 +2644,29 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站金杨路金桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2668,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,12 +2700,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2717,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2755,12 +2763,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2772,12 +2780,12 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站五莲路凌河路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±11分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2811,12 +2819,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2826,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2882,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2891,7 +2899,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站金高路东靖路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2906,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2930,12 +2938,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2993,24 +3001,24 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>08:50采样：该车到重点站航津路地铁站 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3025,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3049,12 +3057,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3064,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3112,24 +3120,24 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站金高路东靖路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -3144,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,12 +3176,12 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3193,7 +3201,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3231,7 +3239,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3248,12 +3256,12 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站张杨北路博兴路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3263,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3287,12 +3295,12 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3350,29 +3358,29 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站金高路行泰路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±14分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3382,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3406,12 +3414,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3421,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3474,26 +3482,22 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站张杨北路博兴路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:10采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3525,12 +3529,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3540,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3588,29 +3592,29 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站金高路行泰路 ETA 47分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3620,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3644,12 +3648,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3659,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3717,19 +3721,19 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站丁香路长柳路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±9分钟</t>
+          <t>10:20采样：该车到重点站花山路杨高北路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3788,7 +3792,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3831,24 +3835,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
+          <t>同车下一次反向发车11:10，减去该车自身同类时段历史终点停站中位数16分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3858,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,12 +3886,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3897,22 +3901,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3950,24 +3954,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±12分钟</t>
+          <t>10:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3977,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,12 +4005,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4026,12 +4030,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4069,26 +4073,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4158,24 +4158,24 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66373D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4188,34 +4188,30 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4229,7 +4225,7 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4239,17 +4235,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4259,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4273,7 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4287,7 +4283,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -4307,22 +4303,26 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>10:20采样：该车到重点站金高路东靖路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4344,47 +4344,868 @@
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站云山路灵山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
+      <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="AC33" s="2" t="inlineStr">
+      <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3597,24 +3597,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3711,24 +3711,24 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站花山路杨高北路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数17分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3835,26 +3835,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车11:10，减去该车自身同类时段历史终点停站中位数16分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:30采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3862,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3886,12 +3882,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3906,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3949,29 +3945,29 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3981,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,12 +4001,12 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4020,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4068,12 +4064,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4085,10 +4081,14 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4188,19 +4188,19 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：10:50采样，终点ETA 8分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr"/>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,17 +4235,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4298,29 +4298,29 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金高路东靖路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4417,29 +4417,29 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站云山路灵山路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4473,12 +4473,12 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4536,27 +4536,31 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4564,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,37 +4592,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4668,12 +4672,12 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±15分钟</t>
+          <t>10:50采样：该车到重点站五莲路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4683,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4707,12 +4711,12 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
@@ -4770,7 +4774,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4780,19 +4784,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4802,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,12 +4830,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4841,22 +4845,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4894,24 +4898,24 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±9分钟</t>
+          <t>11:20采样：该车到重点站巨峰路成园路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4921,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4950,7 +4954,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -4970,12 +4974,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5013,19 +5017,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 45分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
@@ -5036,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,37 +5064,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5098,24 +5102,24 @@
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5128,30 +5132,34 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>11:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5165,47 +5173,872 @@
       <c r="T40" s="2" t="inlineStr"/>
       <c r="U40" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>11:10采样：该车到重点站五莲路凌河路 ETA 43分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X40" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y40" s="2" t="inlineStr">
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z40" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>17/18</t>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,17 +3897,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4422,24 +4422,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4541,12 +4541,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5012,27 +5012,31 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:20采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5040,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,12 +5068,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5084,17 +5088,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5127,29 +5131,29 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站五莲路荷泽路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±10分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5159,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5183,12 +5187,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5198,22 +5202,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5246,29 +5250,29 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11:10采样：该车到重点站五莲路凌河路 ETA 43分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±15分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5278,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5302,12 +5306,12 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
@@ -5317,17 +5321,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5365,29 +5369,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5421,12 +5425,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5436,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5489,19 +5493,19 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 29分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5536,37 +5540,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5604,24 +5608,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±10分钟</t>
+          <t>12:20采样：该车到重点站五莲路凌河路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5631,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5660,7 +5664,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5680,12 +5684,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5723,24 +5727,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>同车下一次反向发车13:30，减去该车自身同类时段历史终点停站中位数22分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5750,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5779,7 +5783,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5789,22 +5793,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5842,22 +5846,26 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>12:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5865,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,17 +5897,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5909,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5984,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6038,7 +6046,602 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC52"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2953,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,17 +4607,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4845,22 +4845,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,17 +5083,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,22 +5202,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5374,24 +5374,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5488,27 +5488,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:20采样，终点ETA 29分钟</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,12 +5544,12 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5565,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5603,29 +5607,29 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站五莲路凌河路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5635,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,12 +5663,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5674,17 +5678,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5722,29 +5726,29 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车13:30，减去该车自身同类时段历史终点停站中位数22分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5754,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5778,12 +5782,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5803,12 +5807,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5841,29 +5845,29 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,12 +5901,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5912,17 +5916,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5960,29 +5964,29 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5992,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6016,12 +6020,12 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6031,22 +6035,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6084,26 +6088,22 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 45分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6203,24 +6203,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
+          <t>同车下一次反向发车14:20，减去该车自身同类时段历史终点停站中位数22分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6322,24 +6322,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±7分钟</t>
+          <t>13:20采样：该车到重点站金杨路枣庄路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6441,24 +6441,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±12分钟</t>
+          <t>13:20采样：该车到重点站张杨北路大同路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,12 +6636,599 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,17 +3897,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,17 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5862,12 +5862,12 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -6093,17 +6093,21 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:20采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6111,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,12 +6139,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6150,17 +6154,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6203,26 +6207,22 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车14:20，减去该车自身同类时段历史终点停站中位数22分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:00采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,12 +6254,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6322,26 +6322,22 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站金杨路枣庄路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:50采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -6349,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,12 +6369,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6398,12 +6394,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6441,26 +6437,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>13:20采样：该车到重点站张杨北路大同路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:00采样，终点ETA 34分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6468,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,12 +6484,12 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
@@ -6507,22 +6499,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6560,24 +6552,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+          <t>14:00采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6587,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6611,12 +6603,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6636,12 +6628,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6679,22 +6671,26 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>14:00采样：该车到重点站巨峰路成园路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6702,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,17 +6722,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6746,17 +6742,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6802,12 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±12分钟</t>
+          <t>14:00采样：该车到重点站金杨路枣庄路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6821,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,12 +6841,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6870,12 +6866,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6994,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7174,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7223,10 +7219,363 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
         <is>
           <t>2/18</t>
         </is>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6202,27 +6202,31 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:00采样，终点ETA 15分钟</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,12 +6258,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6279,12 +6283,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6317,27 +6321,31 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:50采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -6345,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,12 +6377,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6394,12 +6402,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6437,19 +6445,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:00采样，终点ETA 34分钟</t>
+          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 16分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
@@ -6460,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6484,7 +6492,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
@@ -6509,7 +6517,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6547,29 +6555,29 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>14:00采样：该车到重点站五莲路荷泽路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6579,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6603,12 +6611,12 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6628,7 +6636,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6671,26 +6679,22 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>14:00采样：该车到重点站巨峰路成园路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±13分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 53分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6698,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6722,17 +6726,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6742,12 +6746,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6790,24 +6794,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:00采样：该车到重点站金杨路枣庄路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
+          <t>14:20采样：该车到重点站张杨北路金桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6817,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6841,7 +6845,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
@@ -6866,12 +6870,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6909,24 +6913,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数83分钟估算，约±6分钟</t>
+          <t>14:20采样：该车到重点站杨高北路航津路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6936,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6965,7 +6969,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6985,12 +6989,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7028,22 +7032,26 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>14:20采样：该车到重点站和龙路花山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7051,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,17 +7083,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7095,12 +7103,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7143,24 +7151,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±11分钟</t>
+          <t>14:20采样：该车到重点站丁香路民生路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7170,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7194,12 +7202,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7219,12 +7227,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7404,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,24 +7474,24 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7496,34 +7504,34 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7562,20 +7570,139 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>2/18</t>
         </is>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,11 +449,11 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>87.3</t>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,14 +3072,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>87.3</t>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,14 +4016,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,22 +4488,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4650,36 +4650,32 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq26推进至seq34，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>10:50采样：该车到重点站五莲路东陆路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4687,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4695,10 +4691,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq16映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4711,29 +4719,29 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>87.3</t>
@@ -4741,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4855,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4888,36 +4896,32 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程45%处后消失；随后反向物理轨迹由seq23推进至seq28，推进5站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站巨峰路成园路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4933,10 +4937,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>五莲路归昌路</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -4949,37 +4965,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,12 +5109,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5212,7 +5228,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5282,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5466,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,14 +5575,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -5574,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,22 +5694,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5813,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5926,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6045,12 +6061,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,7 +6299,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6353,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6392,14 +6408,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -6407,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6461,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 16分钟</t>
+          <t>SHMAAS末次终点ETA推算：14:30采样，终点ETA 8分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
@@ -6468,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6517,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6560,24 +6576,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6587,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,22 +6642,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6679,19 +6695,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:20采样，终点ETA 53分钟</t>
+          <t>SHMAAS末次终点ETA推算：14:53采样，终点ETA 13分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr"/>
@@ -6702,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,37 +6742,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6789,29 +6805,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站张杨北路金桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6821,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6845,12 +6861,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6870,12 +6886,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6908,29 +6924,29 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站杨高北路航津路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6940,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,12 +6980,12 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -6989,12 +7005,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7032,26 +7048,22 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站和龙路花山路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7059,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,12 +7095,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7108,12 +7120,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7146,29 +7158,29 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站丁香路民生路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7178,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7202,12 +7214,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7227,7 +7239,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7270,22 +7282,26 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>15:10采样：该车到重点站五莲路凌河路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7293,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7317,17 +7333,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7337,17 +7353,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7385,26 +7401,22 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 43分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7412,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7436,12 +7448,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7461,12 +7473,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7504,24 +7516,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
+          <t>15:20采样：该车到重点站杨高北路夏碧路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7531,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7560,7 +7572,7 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7580,12 +7592,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7623,19 +7635,19 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -7650,7 +7662,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7679,32 +7691,976 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站杨高北路夏碧路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y61" s="2" t="inlineStr">
+      <c r="Y65" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>2/18</t>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>78分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,17 +3310,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程45%处后消失；随后反向物理轨迹由seq23推进至seq28，推进5站，达到≥2站确认条件</t>
+          <t>原方向在全程45%处后消失；随后反向物理轨迹由seq23推进至seq39，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,22 +5218,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,22 +5337,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,22 +5456,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,17 +5932,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,22 +6170,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,22 +6876,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7043,27 +7043,31 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 21分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7071,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7095,12 +7099,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7110,17 +7114,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7163,24 +7167,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7190,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,22 +7233,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7277,29 +7281,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>15:10采样：该车到重点站五莲路凌河路 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±15分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,12 +7337,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7348,22 +7352,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7396,27 +7400,31 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：15:20采样，终点ETA 43分钟</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7424,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,12 +7456,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7463,22 +7471,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7511,24 +7519,24 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站杨高北路夏碧路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -7543,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,12 +7575,12 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
@@ -7582,17 +7590,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7630,29 +7638,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7662,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7686,12 +7694,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7701,22 +7709,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7757,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -7759,19 +7767,19 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站杨高北路夏碧路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7781,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7805,12 +7813,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7830,7 +7838,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7868,29 +7876,29 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>15:20采样：该车到重点站金杨路枣庄路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7900,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7924,12 +7932,12 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
@@ -7949,7 +7957,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7992,22 +8000,26 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>16:20采样：该车到重点站云山路灵山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -8015,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8039,17 +8051,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8059,17 +8071,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8107,26 +8119,22 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±15分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8134,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8163,7 +8171,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8183,12 +8191,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8341,24 +8349,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±10分钟</t>
+          <t>16:20采样：该车到重点站五莲路凌河路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8368,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8397,7 +8405,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8417,7 +8425,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8460,24 +8468,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>16:20采样：该车到重点站杨高北路航津路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8487,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8516,7 +8524,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8536,12 +8544,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8579,24 +8587,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数78分钟估算，约±9分钟</t>
+          <t>16:20采样：该车到重点站五莲路凌河路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8606,7 +8614,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8635,32 +8643,980 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站花山路大同路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站云山路灵山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y69" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z69" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>105分钟</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数105分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:38</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>103分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数103分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>108分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数108分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,17 +3782,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,17 +4734,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,22 +5575,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,22 +5694,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,17 +6642,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6757,22 +6757,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6876,22 +6876,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7119,17 +7119,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7774,12 +7774,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7828,17 +7828,17 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7947,22 +7947,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7995,29 +7995,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站云山路灵山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数15分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8066,22 +8066,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8114,27 +8114,31 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8142,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8166,12 +8170,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8181,17 +8185,17 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8229,27 +8233,31 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8257,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,32 +8289,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8344,29 +8352,29 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路凌河路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8376,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8400,12 +8408,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8415,22 +8423,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8463,24 +8471,24 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站杨高北路航津路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -8495,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8519,12 +8527,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8534,17 +8542,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8582,29 +8590,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站五莲路凌河路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±8分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8614,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8638,12 +8646,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8653,7 +8661,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8663,12 +8671,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8701,29 +8709,29 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站花山路大同路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8733,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,12 +8765,12 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8772,22 +8780,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8825,26 +8833,22 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站云山路灵山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8852,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8881,7 +8885,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8901,12 +8905,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8944,22 +8948,26 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8967,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,17 +8999,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9011,17 +9019,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9059,19 +9067,19 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
+          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
@@ -9086,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9115,7 +9123,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9135,7 +9143,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9178,19 +9186,19 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数97分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站巨峰路成园路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -9205,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9234,7 +9242,7 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9254,12 +9262,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9297,24 +9305,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数105分钟估算，约±6分钟</t>
+          <t>17:20采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9324,7 +9332,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9353,7 +9361,7 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9373,12 +9381,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9416,19 +9424,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数103分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9443,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9472,7 +9480,7 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9492,7 +9500,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9535,19 +9543,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数108分钟估算，约±5分钟</t>
+          <t>17:20采样：该车到重点站金高路俱进路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9562,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9591,32 +9599,1091 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站金杨路枣庄路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>17:20采样：该车到重点站杨高北路夏碧路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
+      <c r="Y80" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z77" s="2" t="inlineStr">
+      <c r="Z80" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
+      <c r="AA80" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
-        <is>
-          <t>86.8</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr">
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>18:57</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>106分钟</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数106分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
         <is>
           <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>89.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,17 +3310,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4135,22 +4135,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,22 +5218,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,17 +5818,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,22 +6289,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6647,17 +6647,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,22 +7233,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,22 +7471,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,17 +7590,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7947,22 +7947,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8185,22 +8185,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8547,17 +8547,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8828,27 +8828,31 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:20采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8856,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,12 +8884,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8895,22 +8899,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8943,29 +8947,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±14分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8975,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8999,12 +9003,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9024,12 +9028,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9062,29 +9066,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9094,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9118,12 +9122,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9133,22 +9137,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9181,29 +9185,29 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站巨峰路成园路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9213,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9237,12 +9241,12 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -9252,22 +9256,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9304,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -9317,12 +9321,12 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站巨峰路成园路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9332,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,12 +9360,12 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
@@ -9371,7 +9375,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9424,26 +9428,22 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 19分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9490,17 +9490,17 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9555,14 +9555,10 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金高路俱进路 ETA 24分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 23分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9570,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,12 +9590,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9624,7 +9620,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9662,26 +9658,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站金杨路枣庄路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9689,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,12 +9705,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9738,7 +9730,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9781,26 +9773,22 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:20采样：该车到重点站杨高北路夏碧路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9808,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,12 +9820,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9847,22 +9835,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9912,12 +9900,12 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±9分钟</t>
+          <t>18:10采样：该车到重点站杨高北路洲海路（外高桥保税区） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9927,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9956,7 +9944,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -10019,19 +10007,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±5分钟</t>
+          <t>同车下一次反向发车19:25，减去该车自身同类时段历史终点停站中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10046,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10075,7 +10063,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10085,22 +10073,22 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10253,22 +10241,26 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>18:20采样：该车到重点站五莲路凌河路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10276,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10300,17 +10292,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10320,17 +10312,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10368,24 +10360,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±14分钟</t>
+          <t>18:00采样：该车到重点站杨高北路夏碧路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10395,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10424,7 +10416,7 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10444,7 +10436,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10487,24 +10479,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数106分钟估算，约±10分钟</t>
+          <t>18:20采样：该车到重点站金高路行泰路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10514,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10538,12 +10530,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10629,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10683,7 +10675,824 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>92.4</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,17 +4250,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6767,12 +6767,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6995,17 +6995,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7357,17 +7357,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,17 +7595,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7828,22 +7828,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8304,17 +8304,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8661,22 +8661,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8899,17 +8899,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9142,17 +9142,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9380,17 +9380,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9423,27 +9423,31 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 19分钟</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9451,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,12 +9479,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9495,17 +9499,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9538,12 +9542,12 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -9555,10 +9559,14 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9566,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9590,12 +9598,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9620,7 +9628,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9653,27 +9661,31 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9681,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9705,12 +9717,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9720,22 +9732,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9768,27 +9780,31 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：18:20采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9796,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9820,12 +9836,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9845,12 +9861,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9883,24 +9899,24 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:10采样：该车到重点站杨高北路洲海路（外高桥保税区） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数26分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9915,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9939,12 +9955,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9964,7 +9980,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10002,29 +10018,29 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:07</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车19:25，减去该车自身同类时段历史终点停站中位数18分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10034,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10058,12 +10074,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10083,7 +10099,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10121,27 +10137,31 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10149,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10173,32 +10193,32 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10236,29 +10256,29 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站五莲路凌河路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±13分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10268,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10292,12 +10312,12 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10317,12 +10337,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10355,29 +10375,29 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:00采样：该车到重点站杨高北路夏碧路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10387,7 +10407,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10411,12 +10431,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10436,12 +10456,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10474,29 +10494,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:20采样：该车到重点站金高路行泰路 ETA 31分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10506,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10530,12 +10550,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10555,12 +10575,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10593,27 +10613,31 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10621,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10645,37 +10669,37 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA86" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10713,22 +10737,26 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站杨高北路夏碧路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10736,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10760,17 +10788,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10780,17 +10808,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10828,22 +10856,26 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>同车下一次反向发车20:15，减去该车自身同类时段历史终点停站中位数16分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10851,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10875,32 +10907,32 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10943,19 +10975,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站金高路俱进路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -10970,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10999,7 +11031,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11019,12 +11051,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11062,22 +11094,26 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11085,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11109,17 +11145,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11129,17 +11165,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11177,19 +11213,19 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>19:20采样：该车到重点站金杨路枣庄路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -11204,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11233,7 +11269,7 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11253,12 +11289,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11296,22 +11332,26 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站金高路俱进路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -11319,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11343,17 +11383,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11363,17 +11403,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11438,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11487,12 +11527,480 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>92.4</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
           <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>94.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:09</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>21:31</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>76分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4985,17 +4985,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5228,12 +5228,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,22 +7590,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7828,22 +7828,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9385,7 +9385,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9494,22 +9494,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9732,22 +9732,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10499,24 +10499,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10575,7 +10575,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10618,24 +10618,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10689,17 +10689,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -10742,19 +10742,19 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站杨高北路夏碧路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10788,12 +10788,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10813,12 +10813,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10851,29 +10851,29 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>19:58</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车20:15，减去该车自身同类时段历史终点停站中位数16分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10970,29 +10970,29 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金高路俱进路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11089,24 +11089,24 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站五莲路荷泽路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11208,29 +11208,29 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金杨路枣庄路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
@@ -11289,12 +11289,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -11344,12 +11344,12 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站金高路俱进路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11359,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11398,22 +11398,22 @@
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11446,29 +11446,29 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11570,19 +11570,19 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 34分钟</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11617,37 +11617,37 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>94.2</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11685,26 +11685,22 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 55分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11712,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11736,17 +11732,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11756,17 +11752,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11823,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11866,7 +11862,7 @@
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -11919,24 +11915,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
+          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11946,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11970,37 +11966,390 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>22:04</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X97" s="2" t="inlineStr">
+      <c r="X98" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y97" s="2" t="inlineStr">
+      <c r="Y98" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z97" s="2" t="inlineStr">
+      <c r="Z98" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA97" s="2" t="inlineStr">
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB97" s="2" t="inlineStr">
-        <is>
-          <t>86.3</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr">
-        <is>
-          <t>4/18</t>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-22-浦东78路.xlsx
+++ b/data/export/2026-09-22-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4985,17 +4985,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7828,22 +7828,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8309,17 +8309,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9390,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9693,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9732,22 +9732,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10213,17 +10213,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10689,17 +10689,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11408,12 +11408,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11451,24 +11451,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11565,27 +11565,31 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>20:54</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 34分钟</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11593,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11617,12 +11621,12 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
@@ -11632,22 +11636,22 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11680,27 +11684,31 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 55分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11708,7 +11716,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11732,17 +11740,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11752,17 +11760,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11800,19 +11808,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：21:11采样，终点ETA 28分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
@@ -11823,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11847,17 +11855,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11867,17 +11875,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11910,29 +11918,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11942,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11966,12 +11974,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11991,7 +11999,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12029,29 +12037,29 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12061,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12085,12 +12093,12 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12110,12 +12118,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12188,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12219,22 +12227,22 @@
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12250,7 @@
       <c r="A100" s="2" t="inlineStr"/>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>沪A66373D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -12272,30 +12280,34 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,37 +12331,152 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66373D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X100" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y100" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z100" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>81.2</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>1/18</t>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>
